--- a/Tratamento/src/Dados_limpos/novos/limpo_petlove_20260420_203649.xlsx
+++ b/Tratamento/src/Dados_limpos/novos/limpo_petlove_20260420_203649.xlsx
@@ -5308,7 +5308,7 @@
       </c>
       <c r="P84" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -5540,7 +5540,7 @@
       </c>
       <c r="P88" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -5656,7 +5656,7 @@
       </c>
       <c r="P90" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -6932,7 +6932,7 @@
       </c>
       <c r="P112" t="inlineStr">
         <is>
-          <t>filhote</t>
+          <t>puppy</t>
         </is>
       </c>
     </row>
@@ -6990,7 +6990,7 @@
       </c>
       <c r="P113" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -7106,7 +7106,7 @@
       </c>
       <c r="P115" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -7164,7 +7164,7 @@
       </c>
       <c r="P116" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -7222,7 +7222,7 @@
       </c>
       <c r="P117" t="inlineStr">
         <is>
-          <t>filhote</t>
+          <t>puppy</t>
         </is>
       </c>
     </row>
@@ -7280,7 +7280,7 @@
       </c>
       <c r="P118" t="inlineStr">
         <is>
-          <t>filhote</t>
+          <t>puppy</t>
         </is>
       </c>
     </row>
